--- a/src/DORD/ex01_DORD_infosources.xlsx
+++ b/src/DORD/ex01_DORD_infosources.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="21">
   <si>
     <t>Приортет</t>
   </si>
@@ -73,6 +73,16 @@
   </si>
   <si>
     <t>https://www.consultant.ru/document/cons_doc_LAW_115625/</t>
+  </si>
+  <si>
+    <t>ГОСТ Р 71162-2023
+Услуги общественного питания. Доставка продукции общественного питания по заказам потребителей. Общие требования</t>
+  </si>
+  <si>
+    <t>Максимальная</t>
+  </si>
+  <si>
+    <t>https://internet-law.ru/gosts/gost/81993/</t>
   </si>
 </sst>
 </file>
@@ -117,7 +127,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -130,6 +140,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -412,7 +425,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="5.5546875" customWidth="1"/>
@@ -473,7 +486,7 @@
         <v>10</v>
       </c>
       <c r="C3" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D3" s="3">
         <v>45916</v>
@@ -494,7 +507,7 @@
         <v>12</v>
       </c>
       <c r="C4" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D4" s="3">
         <v>45916</v>
@@ -515,7 +528,7 @@
         <v>14</v>
       </c>
       <c r="C5" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D5" s="1">
         <v>2025</v>
@@ -536,7 +549,7 @@
         <v>16</v>
       </c>
       <c r="C6" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D6" s="3">
         <v>40721</v>
@@ -548,6 +561,36 @@
         <v>17</v>
       </c>
       <c r="G6" s="1"/>
+    </row>
+    <row r="7" spans="1:7" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A7" s="1">
+        <v>6</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" s="1">
+        <v>1</v>
+      </c>
+      <c r="D7" s="3">
+        <v>45444</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="G7" s="1"/>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A8" s="1"/>
+      <c r="B8" s="1"/>
+      <c r="C8" s="1"/>
+      <c r="D8" s="1"/>
+      <c r="E8" s="1"/>
+      <c r="F8" s="1"/>
+      <c r="G8" s="1"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -555,6 +598,7 @@
     <hyperlink ref="F3" r:id="rId2"/>
     <hyperlink ref="F4" r:id="rId3"/>
     <hyperlink ref="F6" r:id="rId4"/>
+    <hyperlink ref="F7" r:id="rId5"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
